--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -3500,9 +3500,8 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="1" max="16383" man="true"/>
-    <brk id="44" max="16383" man="true"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="42" max="16383" man="true"/>
     <brk id="68" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$12</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$111</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$113</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$G$14</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$G$11</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
@@ -2989,81 +2989,63 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="str">
+      <c r="F69" t="s">
+        <v>63</v>
+      </c>
+      <c r="G69" s="19" t="str">
+        <f>IFERROR(INDEX($A$53:$A$62, MATCH(4, $G$53:$G$62, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="str">
         <f>'data'!$A$9</f>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="s">
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="16" t="s">
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="str">
+    <row r="73">
+      <c r="A73" s="14" t="str">
         <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
-      <c r="B71" s="14" t="str">
-        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C71" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D71" s="18"/>
-      <c r="E71" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F71" s="14" t="str">
-        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G71" s="14" t="str">
+      <c r="B73" s="14" t="str">
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C73" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D73" s="18"/>
+      <c r="E73" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F73" s="14" t="str">
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G73" s="14" t="str">
         <f>data!$D$7&amp;" "&amp;data!$B$7</f>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14">
-        <v>1</v>
-      </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14">
-        <v>2</v>
-      </c>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="14">
-        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -3071,12 +3053,12 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -3084,12 +3066,12 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -3097,74 +3079,74 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14">
+        <v>4</v>
+      </c>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="17" t="s">
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14" t="s">
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="16" t="s">
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="14" t="str">
+    <row r="81">
+      <c r="A81" s="14" t="str">
         <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
-      <c r="B79" s="14" t="str">
-        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C79" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D79" s="18"/>
-      <c r="E79" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F79" s="14" t="str">
-        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G79" s="14" t="str">
+      <c r="B81" s="14" t="str">
+        <f>IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C81" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D81" s="18"/>
+      <c r="E81" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F81" s="14" t="str">
+        <f>IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G81" s="14" t="str">
         <f>data!$D$7&amp;" "&amp;data!$B$7</f>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14">
-        <v>1</v>
-      </c>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14">
-        <v>2</v>
-      </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="14">
-        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -3172,12 +3154,12 @@
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
       <c r="G82" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
@@ -3185,12 +3167,12 @@
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
       <c r="G83" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -3198,74 +3180,74 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14">
+        <v>4</v>
+      </c>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="s">
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14" t="s">
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="16" t="s">
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="14" t="str">
+    <row r="89">
+      <c r="A89" s="14" t="str">
         <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
-      <c r="B87" s="14" t="str">
-        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C87" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D87" s="18"/>
-      <c r="E87" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F87" s="14" t="str">
-        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G87" s="14" t="str">
+      <c r="B89" s="14" t="str">
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C89" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D89" s="18"/>
+      <c r="E89" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F89" s="14" t="str">
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G89" s="14" t="str">
         <f>data!$D$8&amp;" "&amp;data!$B$8</f>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="14">
-        <v>1</v>
-      </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="14">
-        <v>2</v>
-      </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="14">
-        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
@@ -3273,12 +3255,12 @@
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
       <c r="G90" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
@@ -3286,12 +3268,12 @@
       <c r="E91" s="18"/>
       <c r="F91" s="18"/>
       <c r="G91" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -3299,194 +3281,220 @@
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
       <c r="G92" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14">
+        <v>4</v>
+      </c>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="13" t="s">
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B97" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C97" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D97" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13" t="s">
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="14" t="str">
-        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
-      </c>
-      <c r="B96" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(F71&gt;B71,AND(F71=B71,E71&gt;C71)),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(F79&gt;B79,AND(F79=B79,E79&gt;C79)),1,0)),0)</f>
-      </c>
-      <c r="C96" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(F71&lt;B71,AND(F71=B71,E71&lt;C71)),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(F79&lt;B79,AND(F79=B79,E79&lt;C79)),1,0)),0)</f>
-      </c>
-      <c r="D96" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),1,0),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),1,0),0)</f>
-      </c>
-      <c r="G96" s="18" t="str">
-        <f>RANK(U96,$U$96:$U$98)+COUNTIF($U$95:U95,U96)</f>
-      </c>
-      <c r="U96" t="str">
-        <f>(B96*1000000000)-(C96*10000000)+(D96*100000)+(B101*1000)-(C101*100)+(D101*10)+(E101*1)-(F101*0.01)</f>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="str">
-        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
-      </c>
-      <c r="B97" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(B71&gt;F71,AND(B71=F71,C71&gt;E71)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(F87&gt;B87,AND(F87=B87,E87&gt;C87)),1,0)),0)</f>
-      </c>
-      <c r="C97" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(B71&lt;F71,AND(B71=F71,C71&lt;E71)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(F87&lt;B87,AND(F87=B87,E87&lt;C87)),1,0)),0)</f>
-      </c>
-      <c r="D97" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),1,0),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),1,0),0)</f>
-      </c>
-      <c r="G97" s="18" t="str">
-        <f>RANK(U97,$U$96:$U$98)+COUNTIF($U$95:U96,U97)</f>
-      </c>
-      <c r="U97" t="str">
-        <f>(B97*1000000000)-(C97*10000000)+(D97*100000)+(B102*1000)-(C102*100)+(D102*10)+(E102*1)-(F102*0.01)</f>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="str">
-        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B98" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(B79&gt;F79,AND(B79=F79,C79&gt;E79)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(B87&gt;F87,AND(B87=F87,C87&gt;E87)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),0,IF(OR(F73&gt;B73,AND(F73=B73,E73&gt;C73)),1,0)),0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),0,IF(OR(F81&gt;B81,AND(F81=B81,E81&gt;C81)),1,0)),0)</f>
       </c>
       <c r="C98" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(B79&lt;F79,AND(B79=F79,C79&lt;E79)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(B87&lt;F87,AND(B87=F87,C87&lt;E87)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),0,IF(OR(F73&lt;B73,AND(F73=B73,E73&lt;C73)),1,0)),0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),0,IF(OR(F81&lt;B81,AND(F81=B81,E81&lt;C81)),1,0)),0)</f>
       </c>
       <c r="D98" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),1,0),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),1,0),0)</f>
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),1,0),0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),1,0),0)</f>
       </c>
       <c r="G98" s="18" t="str">
-        <f>RANK(U98,$U$96:$U$98)+COUNTIF($U$95:U97,U98)</f>
+        <f>RANK(U98,$U$98:$U$100)+COUNTIF($U$97:U97,U98)</f>
       </c>
       <c r="U98" t="str">
         <f>(B98*1000000000)-(C98*10000000)+(D98*100000)+(B103*1000)-(C103*100)+(D103*10)+(E103*1)-(F103*0.01)</f>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="14" t="str">
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
+      </c>
+      <c r="B99" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),0,IF(OR(B73&gt;F73,AND(B73=F73,C73&gt;E73)),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),0,IF(OR(F89&gt;B89,AND(F89=B89,E89&gt;C89)),1,0)),0)</f>
+      </c>
+      <c r="C99" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),0,IF(OR(B73&lt;F73,AND(B73=F73,C73&lt;E73)),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),0,IF(OR(F89&lt;B89,AND(F89=B89,E89&lt;C89)),1,0)),0)</f>
+      </c>
+      <c r="D99" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",D77="X",D77="x",D78="X",D78="x",OR(D73="X",D73="x")),IF(OR(OR(D73="X",D73="x"),AND(B73=F73,C73=E73)),1,0),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),1,0),0)</f>
+      </c>
+      <c r="G99" s="18" t="str">
+        <f>RANK(U99,$U$98:$U$100)+COUNTIF($U$97:U98,U99)</f>
+      </c>
+      <c r="U99" t="str">
+        <f>(B99*1000000000)-(C99*10000000)+(D99*100000)+(B104*1000)-(C104*100)+(D104*10)+(E104*1)-(F104*0.01)</f>
+      </c>
+    </row>
     <row r="100">
-      <c r="A100" s="13"/>
-      <c r="B100" s="13" t="s">
+      <c r="A100" s="14" t="str">
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
+      </c>
+      <c r="B100" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),0,IF(OR(B81&gt;F81,AND(B81=F81,C81&gt;E81)),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),0,IF(OR(B89&gt;F89,AND(B89=F89,C89&gt;E89)),1,0)),0)</f>
+      </c>
+      <c r="C100" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),0,IF(OR(B81&lt;F81,AND(B81=F81,C81&lt;E81)),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),0,IF(OR(B89&lt;F89,AND(B89=F89,C89&lt;E89)),1,0)),0)</f>
+      </c>
+      <c r="D100" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",D85="X",D85="x",D86="X",D86="x",OR(D81="X",D81="x")),IF(OR(OR(D81="X",D81="x"),AND(B81=F81,C81=E81)),1,0),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",D93="X",D93="x",D94="X",D94="x",OR(D89="X",D89="x")),IF(OR(OR(D89="X",D89="x"),AND(B89=F89,C89=E89)),1,0),0)</f>
+      </c>
+      <c r="G100" s="18" t="str">
+        <f>RANK(U100,$U$98:$U$100)+COUNTIF($U$97:U99,U100)</f>
+      </c>
+      <c r="U100" t="str">
+        <f>(B100*1000000000)-(C100*10000000)+(D100*100000)+(B105*1000)-(C105*100)+(D105*10)+(E105*1)-(F105*0.01)</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13"/>
+      <c r="B102" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C102" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D102" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="E100" s="13" t="s">
+      <c r="E102" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F100" s="13" t="s">
+      <c r="F102" s="13" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="str">
-        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
-      </c>
-      <c r="B101" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),F71,0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),F79,0)</f>
-      </c>
-      <c r="C101" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),B71,0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),B79,0)</f>
-      </c>
-      <c r="D101" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),(IF(OR(D72="X",D72="x",AND(COUNTA(B72,C72,E72,F72)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))))),1,0)+IF(OR(D73="X",D73="x",AND(COUNTA(B73,C73,E73,F73)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))))),1,0)+IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),(IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)+IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E101" s="14" t="str">
-        <f>E71+E79</f>
-      </c>
-      <c r="F101" s="14" t="str">
-        <f>C71+C79</f>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="14" t="str">
-        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
-      </c>
-      <c r="B102" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),B71,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),F87,0)</f>
-      </c>
-      <c r="C102" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),F71,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),B87,0)</f>
-      </c>
-      <c r="D102" s="14" t="str">
-        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),(IF(OR(D72="X",D72="x",AND(COUNTA(B72,C72,E72,F72)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))))),1,0)+IF(OR(D73="X",D73="x",AND(COUNTA(B73,C73,E73,F73)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))))),1,0)+IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),(IF(OR(D88="X",D88="x",AND(COUNTA(B88,C88,E88,F88)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))))),1,0)+IF(OR(D89="X",D89="x",AND(COUNTA(B89,C89,E89,F89)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))))),1,0)+IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E102" s="14" t="str">
-        <f>C71+E87</f>
-      </c>
-      <c r="F102" s="14" t="str">
-        <f>E71+C87</f>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="str">
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
+      </c>
+      <c r="B103" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),F73,0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),F81,0)</f>
+      </c>
+      <c r="C103" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),B73,0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),B81,0)</f>
+      </c>
+      <c r="D103" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),(IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)+IF(OR(D77="X",D77="x",AND(COUNTA(B77,C77,E77,F77)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))))),1,0)+IF(OR(D78="X",D78="x",AND(COUNTA(B78,C78,E78,F78)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),(IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)+IF(OR(D85="X",D85="x",AND(COUNTA(B85,C85,E85,F85)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))))),1,0)+IF(OR(D86="X",D86="x",AND(COUNTA(B86,C86,E86,F86)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))))),1,0)),0)</f>
+      </c>
+      <c r="E103" s="14" t="str">
+        <f>E73+E81</f>
+      </c>
+      <c r="F103" s="14" t="str">
+        <f>C73+C81</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="str">
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
+      </c>
+      <c r="B104" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),B73,0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),F89,0)</f>
+      </c>
+      <c r="C104" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),F73,0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),B89,0)</f>
+      </c>
+      <c r="D104" s="14" t="str">
+        <f>IF(OR(COUNTA(B74:C78,E74:F78)&gt;0,OR(D73="X",D73="x"),UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X",UPPER(D77)="X",UPPER(D78)="X"),(IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)+IF(OR(D77="X",D77="x",AND(COUNTA(B77,C77,E77,F77)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))))),1,0)+IF(OR(D78="X",D78="x",AND(COUNTA(B78,C78,E78,F78)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),(IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)+IF(OR(D93="X",D93="x",AND(COUNTA(B93,C93,E93,F93)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))))),1,0)+IF(OR(D94="X",D94="x",AND(COUNTA(B94,C94,E94,F94)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))))),1,0)),0)</f>
+      </c>
+      <c r="E104" s="14" t="str">
+        <f>C73+E89</f>
+      </c>
+      <c r="F104" s="14" t="str">
+        <f>E73+C89</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="str">
         <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
-      <c r="B103" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),B79,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),B87,0)</f>
-      </c>
-      <c r="C103" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),F79,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),F87,0)</f>
-      </c>
-      <c r="D103" s="14" t="str">
-        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),(IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)+IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),(IF(OR(D88="X",D88="x",AND(COUNTA(B88,C88,E88,F88)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))))),1,0)+IF(OR(D89="X",D89="x",AND(COUNTA(B89,C89,E89,F89)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))))),1,0)+IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)),0)</f>
-      </c>
-      <c r="E103" s="14" t="str">
-        <f>C79+C87</f>
-      </c>
-      <c r="F103" s="14" t="str">
-        <f>E79+E87</f>
-      </c>
-    </row>
-    <row r="106">
-      <c r="F106" s="13"/>
-      <c r="G106" s="13" t="s">
+      <c r="B105" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),B81,0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),B89,0)</f>
+      </c>
+      <c r="C105" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),F81,0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),F89,0)</f>
+      </c>
+      <c r="D105" s="14" t="str">
+        <f>IF(OR(COUNTA(B82:C86,E82:F86)&gt;0,OR(D81="X",D81="x"),UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X",UPPER(D85)="X",UPPER(D86)="X"),(IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)+IF(OR(D85="X",D85="x",AND(COUNTA(B85,C85,E85,F85)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))))),1,0)+IF(OR(D86="X",D86="x",AND(COUNTA(B86,C86,E86,F86)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B90:C94,E90:F94)&gt;0,OR(D89="X",D89="x"),UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X",UPPER(D93)="X",UPPER(D94)="X"),(IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)+IF(OR(D93="X",D93="x",AND(COUNTA(B93,C93,E93,F93)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))))),1,0)+IF(OR(D94="X",D94="x",AND(COUNTA(B94,C94,E94,F94)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))))),1,0)),0)</f>
+      </c>
+      <c r="E105" s="14" t="str">
+        <f>C81+C89</f>
+      </c>
+      <c r="F105" s="14" t="str">
+        <f>E81+E89</f>
+      </c>
+    </row>
+    <row r="108">
+      <c r="F108" s="13"/>
+      <c r="G108" s="13" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="F107" t="s">
-        <v>60</v>
-      </c>
-      <c r="G107" s="19" t="str">
-        <f>IFERROR(INDEX($A$96:$A$103, MATCH(1, $G$96:$G$103, 0)), "-")</f>
-      </c>
-    </row>
-    <row r="108">
-      <c r="F108" t="s">
-        <v>61</v>
-      </c>
-      <c r="G108" s="19" t="str">
-        <f>IFERROR(INDEX($A$96:$A$103, MATCH(2, $G$96:$G$103, 0)), "-")</f>
       </c>
     </row>
     <row r="109">
       <c r="F109" t="s">
+        <v>60</v>
+      </c>
+      <c r="G109" s="19" t="str">
+        <f>IFERROR(INDEX($A$98:$A$105, MATCH(1, $G$98:$G$105, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="F110" t="s">
+        <v>61</v>
+      </c>
+      <c r="G110" s="19" t="str">
+        <f>IFERROR(INDEX($A$98:$A$105, MATCH(2, $G$98:$G$105, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="F111" t="s">
         <v>62</v>
       </c>
-      <c r="G109" s="19" t="str">
-        <f>IFERROR(INDEX($A$96:$A$103, MATCH(3, $G$96:$G$103, 0)), "-")</f>
+      <c r="G111" s="19" t="str">
+        <f>IFERROR(INDEX($A$98:$A$105, MATCH(3, $G$98:$G$105, 0)), "-")</f>
       </c>
     </row>
   </sheetData>
@@ -3496,13 +3504,13 @@
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A71:G71"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="42" max="16383" man="true"/>
-    <brk id="68" max="16383" man="true"/>
+    <brk id="70" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -3599,10 +3607,10 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G109)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G110)</f>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -3751,10 +3759,10 @@
         <v>54</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G109)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G110)</f>
       </c>
       <c r="J11" s="14" t="s">
         <v>54</v>
@@ -4356,7 +4364,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G109)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -4478,7 +4486,7 @@
     </row>
     <row r="11">
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G110)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -276,94 +276,94 @@
   </numFmts>
   <fonts count="13">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="250"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1334,16 +1334,16 @@
         <v>12</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
@@ -1360,16 +1360,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -1438,16 +1438,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
